--- a/MMORPG_SERVER/Data/Excel/UnitDefine.xlsx
+++ b/MMORPG_SERVER/Data/Excel/UnitDefine.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\game\MMORPG_GAME_SERVER\MMORPG_SERVER\Data\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BAB892EB-8392-46E8-A840-FE7765BD21AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{092B9308-607C-4F41-B5A3-947C1911B5FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="42">
   <si>
     <t>ID</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -180,6 +180,18 @@
   </si>
   <si>
     <t>int[]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>小红药</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>物品</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Entity/Item/Hp1</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -514,7 +526,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I7"/>
+  <dimension ref="A1:I8"/>
   <sheetFormatPr defaultColWidth="17.875" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="16384" width="17.875" style="1"/>
@@ -711,6 +723,20 @@
         <v>35</v>
       </c>
     </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A8" s="1">
+        <v>5</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/MMORPG_SERVER/Data/Excel/UnitDefine.xlsx
+++ b/MMORPG_SERVER/Data/Excel/UnitDefine.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\game\MMORPG_GAME_SERVER\MMORPG_SERVER\Data\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{092B9308-607C-4F41-B5A3-947C1911B5FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A4DE692-C79F-4EFD-899D-61274555B299}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="46">
   <si>
     <t>ID</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -191,7 +191,23 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Entity/Item/Hp1</t>
+    <t>Entity/RemotePlayer/remotePlayer1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Entity/RemotePlayer/remotePlayer2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Entity/RemotePlayer/remotePlayer3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Entity/RemotePlayer/remotePlayer4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Entity/Item/item1</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -529,7 +545,9 @@
   <dimension ref="A1:I8"/>
   <sheetFormatPr defaultColWidth="17.875" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="16384" width="17.875" style="1"/>
+    <col min="1" max="5" width="17.875" style="1"/>
+    <col min="6" max="6" width="40.125" style="1" customWidth="1"/>
+    <col min="7" max="16384" width="17.875" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.2">
@@ -635,6 +653,9 @@
       <c r="E4" s="2" t="s">
         <v>20</v>
       </c>
+      <c r="F4" s="1" t="s">
+        <v>41</v>
+      </c>
       <c r="G4" s="1">
         <v>1200</v>
       </c>
@@ -661,6 +682,9 @@
       <c r="E5" s="2" t="s">
         <v>23</v>
       </c>
+      <c r="F5" s="1" t="s">
+        <v>42</v>
+      </c>
       <c r="G5" s="1">
         <v>800</v>
       </c>
@@ -687,6 +711,9 @@
       <c r="E6" s="3" t="s">
         <v>32</v>
       </c>
+      <c r="F6" s="1" t="s">
+        <v>43</v>
+      </c>
       <c r="G6" s="1">
         <v>1000</v>
       </c>
@@ -713,6 +740,9 @@
       <c r="E7" s="3" t="s">
         <v>31</v>
       </c>
+      <c r="F7" s="1" t="s">
+        <v>44</v>
+      </c>
       <c r="G7" s="1">
         <v>1500</v>
       </c>
@@ -734,7 +764,7 @@
         <v>40</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
     </row>
   </sheetData>

--- a/MMORPG_SERVER/Data/Excel/UnitDefine.xlsx
+++ b/MMORPG_SERVER/Data/Excel/UnitDefine.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\game\MMORPG_GAME_SERVER\MMORPG_SERVER\Data\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A4DE692-C79F-4EFD-899D-61274555B299}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C97F2D2A-74E7-49C9-BEA0-4E1D6C6222C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="52">
   <si>
     <t>ID</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -208,6 +208,30 @@
   </si>
   <si>
     <t>Entity/Item/item1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>毒蝎龙</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>敌人</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Entity/Monster/monster1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>OriginalPosition</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>生成点</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[18,0,95]</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -542,7 +566,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I8"/>
+  <dimension ref="A1:J9"/>
   <sheetFormatPr defaultColWidth="17.875" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="5" width="17.875" style="1"/>
@@ -550,7 +574,7 @@
     <col min="7" max="16384" width="17.875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -578,8 +602,11 @@
       <c r="I1" s="1" t="s">
         <v>33</v>
       </c>
+      <c r="J1" s="1" t="s">
+        <v>49</v>
+      </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>8</v>
       </c>
@@ -607,8 +634,11 @@
       <c r="I2" s="1" t="s">
         <v>38</v>
       </c>
+      <c r="J2" s="1" t="s">
+        <v>38</v>
+      </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>10</v>
       </c>
@@ -636,8 +666,11 @@
       <c r="I3" s="1" t="s">
         <v>34</v>
       </c>
+      <c r="J3" s="1" t="s">
+        <v>50</v>
+      </c>
     </row>
-    <row r="4" spans="1:9" ht="57" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:10" ht="57" x14ac:dyDescent="0.2">
       <c r="A4" s="1">
         <v>1</v>
       </c>
@@ -666,7 +699,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="5" spans="1:9" ht="57.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:10" ht="57.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="1">
         <v>2</v>
       </c>
@@ -695,7 +728,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="6" spans="1:9" ht="56.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:10" ht="56.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="1">
         <v>3</v>
       </c>
@@ -724,7 +757,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="7" spans="1:9" ht="62.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:10" ht="62.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="1">
         <v>4</v>
       </c>
@@ -753,7 +786,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A8" s="1">
         <v>5</v>
       </c>
@@ -765,6 +798,29 @@
       </c>
       <c r="F8" s="1" t="s">
         <v>45</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A9" s="1">
+        <v>6</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="G9" s="1">
+        <v>300</v>
+      </c>
+      <c r="I9" s="1">
+        <v>30</v>
+      </c>
+      <c r="J9" s="1" t="s">
+        <v>51</v>
       </c>
     </row>
   </sheetData>

--- a/MMORPG_SERVER/Data/Excel/UnitDefine.xlsx
+++ b/MMORPG_SERVER/Data/Excel/UnitDefine.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\game\MMORPG_GAME_SERVER\MMORPG_SERVER\Data\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C97F2D2A-74E7-49C9-BEA0-4E1D6C6222C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E20EB4D-F7E0-44F0-BDC7-EBDF4327528D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="56">
   <si>
     <t>ID</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -231,7 +231,23 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>[18,0,95]</t>
+    <t>MovePosition</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>巡逻点</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>int[][]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[ 18, 0, 95 ]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[ 18, 0, 100 ],[ 25, 0, 100 ]</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -566,15 +582,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J9"/>
+  <dimension ref="A1:K9"/>
   <sheetFormatPr defaultColWidth="17.875" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="5" width="17.875" style="1"/>
     <col min="6" max="6" width="40.125" style="1" customWidth="1"/>
-    <col min="7" max="16384" width="17.875" style="1"/>
+    <col min="7" max="9" width="17.875" style="1"/>
+    <col min="10" max="10" width="17.875" style="1" customWidth="1"/>
+    <col min="11" max="11" width="30.625" style="1" customWidth="1"/>
+    <col min="12" max="16384" width="17.875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -605,8 +624,11 @@
       <c r="J1" s="1" t="s">
         <v>49</v>
       </c>
+      <c r="K1" s="1" t="s">
+        <v>51</v>
+      </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>8</v>
       </c>
@@ -637,8 +659,11 @@
       <c r="J2" s="1" t="s">
         <v>38</v>
       </c>
+      <c r="K2" s="1" t="s">
+        <v>53</v>
+      </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>10</v>
       </c>
@@ -669,8 +694,11 @@
       <c r="J3" s="1" t="s">
         <v>50</v>
       </c>
+      <c r="K3" s="1" t="s">
+        <v>52</v>
+      </c>
     </row>
-    <row r="4" spans="1:10" ht="57" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:11" ht="57" x14ac:dyDescent="0.2">
       <c r="A4" s="1">
         <v>1</v>
       </c>
@@ -699,7 +727,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="5" spans="1:10" ht="57.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:11" ht="57.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="1">
         <v>2</v>
       </c>
@@ -728,7 +756,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="6" spans="1:10" ht="56.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:11" ht="56.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="1">
         <v>3</v>
       </c>
@@ -757,7 +785,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="7" spans="1:10" ht="62.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:11" ht="62.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="1">
         <v>4</v>
       </c>
@@ -786,7 +814,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A8" s="1">
         <v>5</v>
       </c>
@@ -800,7 +828,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A9" s="1">
         <v>6</v>
       </c>
@@ -820,7 +848,10 @@
         <v>30</v>
       </c>
       <c r="J9" s="1" t="s">
-        <v>51</v>
+        <v>54</v>
+      </c>
+      <c r="K9" s="1" t="s">
+        <v>55</v>
       </c>
     </row>
   </sheetData>

--- a/MMORPG_SERVER/Data/Excel/UnitDefine.xlsx
+++ b/MMORPG_SERVER/Data/Excel/UnitDefine.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\game\MMORPG_GAME_SERVER\MMORPG_SERVER\Data\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E20EB4D-F7E0-44F0-BDC7-EBDF4327528D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1643D6FE-E01E-4457-B327-83CEBC80DC10}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="63">
   <si>
     <t>ID</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -167,18 +167,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>20,30,40</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>15,20,25</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>20,25,35</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>int[]</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -247,7 +235,47 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>[ 18, 0, 100 ],[ 25, 0, 100 ]</t>
+    <t>石头人</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Entity/Monster/monster2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[ 20, 30, 40 ]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[ 15, 20, 25 ]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[ 20, 25, 35 ]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[ 30 ]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[ 50 ]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[ -30, -3, 90 ]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">[[ -8, -3, 95 ],[ -8, -3, 105 ],[ 12, -3, 95 ]]    </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[[ -30, -3, 100],[ -10, -3, 100],[ -10, -3, 90 ]]</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -582,14 +610,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K9"/>
+  <dimension ref="A1:K10"/>
   <sheetFormatPr defaultColWidth="17.875" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="5" width="17.875" style="1"/>
     <col min="6" max="6" width="40.125" style="1" customWidth="1"/>
     <col min="7" max="9" width="17.875" style="1"/>
     <col min="10" max="10" width="17.875" style="1" customWidth="1"/>
-    <col min="11" max="11" width="30.625" style="1" customWidth="1"/>
+    <col min="11" max="11" width="37.75" style="1" customWidth="1"/>
     <col min="12" max="16384" width="17.875" style="1"/>
   </cols>
   <sheetData>
@@ -622,10 +650,10 @@
         <v>33</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.2">
@@ -654,13 +682,13 @@
         <v>8</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.2">
@@ -692,10 +720,10 @@
         <v>34</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
     </row>
     <row r="4" spans="1:11" ht="57" x14ac:dyDescent="0.2">
@@ -715,7 +743,7 @@
         <v>20</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="G4" s="1">
         <v>1200</v>
@@ -724,7 +752,7 @@
         <v>80</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>37</v>
+        <v>56</v>
       </c>
     </row>
     <row r="5" spans="1:11" ht="57.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -744,7 +772,7 @@
         <v>23</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="G5" s="1">
         <v>800</v>
@@ -753,7 +781,7 @@
         <v>100</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>36</v>
+        <v>55</v>
       </c>
     </row>
     <row r="6" spans="1:11" ht="56.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -773,7 +801,7 @@
         <v>32</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="G6" s="1">
         <v>1000</v>
@@ -782,7 +810,7 @@
         <v>80</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>36</v>
+        <v>55</v>
       </c>
     </row>
     <row r="7" spans="1:11" ht="62.45" customHeight="1" x14ac:dyDescent="0.2">
@@ -802,7 +830,7 @@
         <v>31</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="G7" s="1">
         <v>1500</v>
@@ -811,7 +839,7 @@
         <v>60</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>35</v>
+        <v>54</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.2">
@@ -819,13 +847,22 @@
         <v>5</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>45</v>
+        <v>42</v>
+      </c>
+      <c r="G8" s="1">
+        <v>0</v>
+      </c>
+      <c r="H8" s="1">
+        <v>0</v>
+      </c>
+      <c r="I8" s="1" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.2">
@@ -833,25 +870,57 @@
         <v>6</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="G9" s="1">
         <v>300</v>
       </c>
-      <c r="I9" s="1">
-        <v>30</v>
+      <c r="H9" s="1">
+        <v>0</v>
+      </c>
+      <c r="I9" s="1" t="s">
+        <v>57</v>
       </c>
       <c r="J9" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="K9" s="1" t="s">
-        <v>55</v>
+        <v>51</v>
+      </c>
+      <c r="K9" s="2" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A10" s="1">
+        <v>7</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="G10" s="1">
+        <v>500</v>
+      </c>
+      <c r="H10" s="1">
+        <v>0</v>
+      </c>
+      <c r="I10" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="J10" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="K10" s="2" t="s">
+        <v>62</v>
       </c>
     </row>
   </sheetData>

--- a/MMORPG_SERVER/Data/Excel/UnitDefine.xlsx
+++ b/MMORPG_SERVER/Data/Excel/UnitDefine.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\game\MMORPG_GAME_SERVER\MMORPG_SERVER\Data\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1643D6FE-E01E-4457-B327-83CEBC80DC10}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{442BC4A1-DAA4-4331-9D53-7D0D9A98522A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="68">
   <si>
     <t>ID</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -231,10 +231,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>[ 18, 0, 95 ]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>石头人</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -271,11 +267,35 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve">[[ -8, -3, 95 ],[ -8, -3, 105 ],[ 12, -3, 95 ]]    </t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>[[ -30, -3, 100],[ -10, -3, 100],[ -10, -3, 90 ]]</t>
+    <t>[ 18, -2, 95 ]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">[[ -5, -4, 90 ],[ 15, -4, 95 ],[ 10, -4, 102 ]]    </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[[ -30, -3, 100],[ -10, -3, 95],[ -15, -3, 97 ]]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>RequireExp</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[20, 30, 50, 100, 150, 200, 250, 300, 350, 400]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>升级所需经验值</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>KilledExp</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>击败后可以获得的经验值</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -610,7 +630,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K10"/>
+  <dimension ref="A1:M10"/>
   <sheetFormatPr defaultColWidth="17.875" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="5" width="17.875" style="1"/>
@@ -618,10 +638,12 @@
     <col min="7" max="9" width="17.875" style="1"/>
     <col min="10" max="10" width="17.875" style="1" customWidth="1"/>
     <col min="11" max="11" width="37.75" style="1" customWidth="1"/>
-    <col min="12" max="16384" width="17.875" style="1"/>
+    <col min="12" max="12" width="37.125" style="1" customWidth="1"/>
+    <col min="13" max="13" width="21.875" style="1" customWidth="1"/>
+    <col min="14" max="16384" width="17.875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -655,8 +677,14 @@
       <c r="K1" s="1" t="s">
         <v>48</v>
       </c>
+      <c r="L1" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>66</v>
+      </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>8</v>
       </c>
@@ -690,8 +718,14 @@
       <c r="K2" s="1" t="s">
         <v>50</v>
       </c>
+      <c r="L2" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>10</v>
       </c>
@@ -725,8 +759,14 @@
       <c r="K3" s="1" t="s">
         <v>49</v>
       </c>
+      <c r="L3" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="M3" s="1" t="s">
+        <v>67</v>
+      </c>
     </row>
-    <row r="4" spans="1:11" ht="57" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:13" ht="57" x14ac:dyDescent="0.2">
       <c r="A4" s="1">
         <v>1</v>
       </c>
@@ -752,10 +792,16 @@
         <v>80</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
+      </c>
+      <c r="L4" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="M4" s="1">
+        <v>100</v>
       </c>
     </row>
-    <row r="5" spans="1:11" ht="57.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:13" ht="57.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="1">
         <v>2</v>
       </c>
@@ -781,10 +827,16 @@
         <v>100</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
+      </c>
+      <c r="L5" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="M5" s="1">
+        <v>100</v>
       </c>
     </row>
-    <row r="6" spans="1:11" ht="56.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:13" ht="56.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="1">
         <v>3</v>
       </c>
@@ -810,10 +862,16 @@
         <v>80</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
+      </c>
+      <c r="L6" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="M6" s="1">
+        <v>100</v>
       </c>
     </row>
-    <row r="7" spans="1:11" ht="62.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:13" ht="62.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="1">
         <v>4</v>
       </c>
@@ -839,10 +897,16 @@
         <v>60</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
+      </c>
+      <c r="L7" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="M7" s="1">
+        <v>100</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A8" s="1">
         <v>5</v>
       </c>
@@ -862,10 +926,10 @@
         <v>0</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A9" s="1">
         <v>6</v>
       </c>
@@ -885,27 +949,30 @@
         <v>0</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="J9" s="1" t="s">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="K9" s="2" t="s">
         <v>61</v>
       </c>
+      <c r="M9" s="1">
+        <v>30</v>
+      </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A10" s="1">
         <v>7</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>44</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="G10" s="1">
         <v>500</v>
@@ -914,13 +981,16 @@
         <v>0</v>
       </c>
       <c r="I10" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="J10" s="1" t="s">
         <v>58</v>
-      </c>
-      <c r="J10" s="1" t="s">
-        <v>59</v>
       </c>
       <c r="K10" s="2" t="s">
         <v>62</v>
+      </c>
+      <c r="M10" s="1">
+        <v>50</v>
       </c>
     </row>
   </sheetData>

--- a/MMORPG_SERVER/Data/Excel/UnitDefine.xlsx
+++ b/MMORPG_SERVER/Data/Excel/UnitDefine.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\game\MMORPG_GAME_SERVER\MMORPG_SERVER\Data\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{442BC4A1-DAA4-4331-9D53-7D0D9A98522A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0970235-1BE2-4C77-8A20-CB53EE5D8516}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="76">
   <si>
     <t>ID</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -151,14 +151,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>将巨剑猛力砸向地面，引发扇形范围的岩刺爆发，对近距离敌人造成击飞效果。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>向四周发射毒箭，被打中的敌人将受到持续伤害。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>AttackDemage</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -259,26 +251,10 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>[ -30, -3, 90 ]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>[]</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>[ 18, -2, 95 ]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">[[ -5, -4, 90 ],[ 15, -4, 95 ],[ 10, -4, 102 ]]    </t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>[[ -30, -3, 100],[ -10, -3, 95],[ -15, -3, 97 ]]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>RequireExp</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -296,6 +272,62 @@
   </si>
   <si>
     <t>击败后可以获得的经验值</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[ 20, -2, 95 ]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[ -30, -2, 95 ]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">[ [ -5, -4, 95 ],[ 15, -4, 93 ],[ 6, -4, 100 ] ]    </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[ [ -10, -4, 93 ],[ -6, -4, 109 ],[ -25, -4, 95 ] ]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>向四周发射毒箭，被打中的敌人将受到持续伤害。冷却13秒</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>将巨剑猛力砸向地面，引发扇形范围的岩刺爆发，对近距离敌人造成击飞效果。冷却15秒。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SkillInterval</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>技能冷却时间</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SkillIconPath</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>技能图标路径</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>UI/SkillIcon/Character1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>UI/SkillIcon/Character2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>UI/SkillIcon/Character3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>UI/SkillIcon/Character4</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -630,7 +662,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M10"/>
+  <dimension ref="A1:O10"/>
   <sheetFormatPr defaultColWidth="17.875" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="5" width="17.875" style="1"/>
@@ -640,10 +672,12 @@
     <col min="11" max="11" width="37.75" style="1" customWidth="1"/>
     <col min="12" max="12" width="37.125" style="1" customWidth="1"/>
     <col min="13" max="13" width="21.875" style="1" customWidth="1"/>
-    <col min="14" max="16384" width="17.875" style="1"/>
+    <col min="14" max="14" width="17.875" style="1"/>
+    <col min="15" max="15" width="21.75" style="1" customWidth="1"/>
+    <col min="16" max="16384" width="17.875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -669,22 +703,28 @@
         <v>7</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="J1" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="K1" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="K1" s="1" t="s">
-        <v>48</v>
-      </c>
       <c r="L1" s="1" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>66</v>
+        <v>60</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>70</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>8</v>
       </c>
@@ -710,22 +750,28 @@
         <v>8</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="M2" s="1" t="s">
         <v>8</v>
       </c>
+      <c r="N2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>10</v>
       </c>
@@ -751,22 +797,28 @@
         <v>17</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="J3" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="K3" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="K3" s="1" t="s">
-        <v>49</v>
-      </c>
       <c r="L3" s="1" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="M3" s="1" t="s">
-        <v>67</v>
+        <v>61</v>
+      </c>
+      <c r="N3" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="O3" s="1" t="s">
+        <v>71</v>
       </c>
     </row>
-    <row r="4" spans="1:13" ht="57" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:15" ht="57" x14ac:dyDescent="0.2">
       <c r="A4" s="1">
         <v>1</v>
       </c>
@@ -783,7 +835,7 @@
         <v>20</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G4" s="1">
         <v>1200</v>
@@ -792,16 +844,22 @@
         <v>80</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="L4" s="1" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="M4" s="1">
         <v>100</v>
       </c>
+      <c r="N4" s="1">
+        <v>12</v>
+      </c>
+      <c r="O4" s="1" t="s">
+        <v>72</v>
+      </c>
     </row>
-    <row r="5" spans="1:13" ht="57.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:15" ht="57.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="1">
         <v>2</v>
       </c>
@@ -818,7 +876,7 @@
         <v>23</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="G5" s="1">
         <v>800</v>
@@ -827,16 +885,22 @@
         <v>100</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="L5" s="1" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="M5" s="1">
         <v>100</v>
       </c>
+      <c r="N5" s="1">
+        <v>10</v>
+      </c>
+      <c r="O5" s="1" t="s">
+        <v>73</v>
+      </c>
     </row>
-    <row r="6" spans="1:13" ht="56.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:15" ht="56.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="1">
         <v>3</v>
       </c>
@@ -850,10 +914,10 @@
         <v>29</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>32</v>
+        <v>66</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="G6" s="1">
         <v>1000</v>
@@ -862,16 +926,22 @@
         <v>80</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="L6" s="1" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="M6" s="1">
         <v>100</v>
       </c>
+      <c r="N6" s="1">
+        <v>13</v>
+      </c>
+      <c r="O6" s="1" t="s">
+        <v>74</v>
+      </c>
     </row>
-    <row r="7" spans="1:13" ht="62.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:15" ht="62.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="1">
         <v>4</v>
       </c>
@@ -885,10 +955,10 @@
         <v>30</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>31</v>
+        <v>67</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="G7" s="1">
         <v>1500</v>
@@ -897,27 +967,33 @@
         <v>60</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="L7" s="1" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="M7" s="1">
         <v>100</v>
       </c>
+      <c r="N7" s="1">
+        <v>15</v>
+      </c>
+      <c r="O7" s="1" t="s">
+        <v>75</v>
+      </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A8" s="1">
         <v>5</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="G8" s="1">
         <v>0</v>
@@ -926,21 +1002,21 @@
         <v>0</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A9" s="1">
         <v>6</v>
       </c>
       <c r="B9" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F9" s="1" t="s">
         <v>43</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="F9" s="1" t="s">
-        <v>45</v>
       </c>
       <c r="G9" s="1">
         <v>300</v>
@@ -949,30 +1025,30 @@
         <v>0</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="J9" s="1" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="K9" s="2" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="M9" s="1">
         <v>30</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A10" s="1">
         <v>7</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="G10" s="1">
         <v>500</v>
@@ -981,13 +1057,13 @@
         <v>0</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="J10" s="1" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="K10" s="2" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="M10" s="1">
         <v>50</v>

--- a/MMORPG_SERVER/Data/Excel/UnitDefine.xlsx
+++ b/MMORPG_SERVER/Data/Excel/UnitDefine.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\game\MMORPG_GAME_SERVER\MMORPG_SERVER\Data\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0970235-1BE2-4C77-8A20-CB53EE5D8516}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54FB3D7B-3CFB-490F-A6C7-7E491D2F3D17}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="85">
   <si>
     <t>ID</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -328,6 +328,42 @@
   </si>
   <si>
     <t>UI/SkillIcon/Character4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>老魔弹</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>导弹</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Entity/Missile/character2Skill</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[100]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>InteractEffectPath</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>触发后的特效路径</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Entity/Effect/character2Skill</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SkillUnitId</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>技能的实体Id</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -662,7 +698,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O10"/>
+  <dimension ref="A1:Q11"/>
   <sheetFormatPr defaultColWidth="17.875" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="5" width="17.875" style="1"/>
@@ -674,10 +710,11 @@
     <col min="13" max="13" width="21.875" style="1" customWidth="1"/>
     <col min="14" max="14" width="17.875" style="1"/>
     <col min="15" max="15" width="21.75" style="1" customWidth="1"/>
-    <col min="16" max="16384" width="17.875" style="1"/>
+    <col min="16" max="16" width="22.875" style="1" customWidth="1"/>
+    <col min="17" max="16384" width="17.875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -723,8 +760,14 @@
       <c r="O1" s="1" t="s">
         <v>70</v>
       </c>
+      <c r="P1" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>83</v>
+      </c>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>8</v>
       </c>
@@ -770,8 +813,14 @@
       <c r="O2" s="1" t="s">
         <v>9</v>
       </c>
+      <c r="P2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>10</v>
       </c>
@@ -817,8 +866,14 @@
       <c r="O3" s="1" t="s">
         <v>71</v>
       </c>
+      <c r="P3" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="Q3" s="1" t="s">
+        <v>84</v>
+      </c>
     </row>
-    <row r="4" spans="1:15" ht="57" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:17" ht="57" x14ac:dyDescent="0.2">
       <c r="A4" s="1">
         <v>1</v>
       </c>
@@ -859,7 +914,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="5" spans="1:15" ht="57.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:17" ht="57.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="1">
         <v>2</v>
       </c>
@@ -899,8 +954,11 @@
       <c r="O5" s="1" t="s">
         <v>73</v>
       </c>
+      <c r="Q5" s="1">
+        <v>8</v>
+      </c>
     </row>
-    <row r="6" spans="1:15" ht="56.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:17" ht="56.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="1">
         <v>3</v>
       </c>
@@ -941,7 +999,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="7" spans="1:15" ht="62.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:17" ht="62.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="1">
         <v>4</v>
       </c>
@@ -982,7 +1040,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A8" s="1">
         <v>5</v>
       </c>
@@ -1005,7 +1063,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A9" s="1">
         <v>6</v>
       </c>
@@ -1037,7 +1095,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A10" s="1">
         <v>7</v>
       </c>
@@ -1067,6 +1125,26 @@
       </c>
       <c r="M10" s="1">
         <v>50</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A11" s="1">
+        <v>8</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="I11" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="P11" s="1" t="s">
+        <v>82</v>
       </c>
     </row>
   </sheetData>

--- a/MMORPG_SERVER/Data/Excel/UnitDefine.xlsx
+++ b/MMORPG_SERVER/Data/Excel/UnitDefine.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\game\MMORPG_GAME_SERVER\MMORPG_SERVER\Data\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54FB3D7B-3CFB-490F-A6C7-7E491D2F3D17}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3596C37-D76F-42A1-8C59-DBB7081A0DFE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="92">
   <si>
     <t>ID</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -364,6 +364,34 @@
   </si>
   <si>
     <t>技能的实体Id</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>山崩地裂</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[50]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Entity/Missile/character4Skill</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>火球</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Entity/Missile/character3Skill</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[60]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Entity/Effect/character3Skill</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -698,7 +726,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Q11"/>
+  <dimension ref="A1:Q13"/>
   <sheetFormatPr defaultColWidth="17.875" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="5" width="17.875" style="1"/>
@@ -998,6 +1026,9 @@
       <c r="O6" s="1" t="s">
         <v>74</v>
       </c>
+      <c r="Q6" s="1">
+        <v>10</v>
+      </c>
     </row>
     <row r="7" spans="1:17" ht="62.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="1">
@@ -1039,6 +1070,9 @@
       <c r="O7" s="1" t="s">
         <v>75</v>
       </c>
+      <c r="Q7" s="1">
+        <v>9</v>
+      </c>
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A8" s="1">
@@ -1145,6 +1179,43 @@
       </c>
       <c r="P11" s="1" t="s">
         <v>82</v>
+      </c>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A12" s="1">
+        <v>9</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="I12" s="1" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A13" s="1">
+        <v>10</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="I13" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="P13" s="1" t="s">
+        <v>91</v>
       </c>
     </row>
   </sheetData>

--- a/MMORPG_SERVER/Data/Excel/UnitDefine.xlsx
+++ b/MMORPG_SERVER/Data/Excel/UnitDefine.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\game\MMORPG_GAME_SERVER\MMORPG_SERVER\Data\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3596C37-D76F-42A1-8C59-DBB7081A0DFE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9C8BB70-76F1-442C-B1F8-8E7F662E4DF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="94">
   <si>
     <t>ID</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -335,10 +335,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>导弹</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>Entity/Missile/character2Skill</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -392,6 +388,18 @@
   </si>
   <si>
     <t>Entity/Effect/character3Skill</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>裂地劈</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>技能</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Entity/Missile/character1Skill</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -726,7 +734,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Q13"/>
+  <dimension ref="A1:Q14"/>
   <sheetFormatPr defaultColWidth="17.875" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="5" width="17.875" style="1"/>
@@ -789,10 +797,10 @@
         <v>70</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.2">
@@ -895,10 +903,10 @@
         <v>71</v>
       </c>
       <c r="P3" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="Q3" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="4" spans="1:17" ht="57" x14ac:dyDescent="0.2">
@@ -941,6 +949,9 @@
       <c r="O4" s="1" t="s">
         <v>72</v>
       </c>
+      <c r="Q4" s="1">
+        <v>11</v>
+      </c>
     </row>
     <row r="5" spans="1:17" ht="57.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="1">
@@ -1169,16 +1180,16 @@
         <v>76</v>
       </c>
       <c r="C11" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="F11" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="F11" s="1" t="s">
+      <c r="I11" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="I11" s="1" t="s">
-        <v>79</v>
-      </c>
       <c r="P11" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.2">
@@ -1186,16 +1197,16 @@
         <v>9</v>
       </c>
       <c r="B12" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="I12" s="1" t="s">
         <v>85</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="F12" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="I12" s="1" t="s">
-        <v>86</v>
       </c>
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.2">
@@ -1203,19 +1214,36 @@
         <v>10</v>
       </c>
       <c r="B13" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="F13" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="C13" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="F13" s="1" t="s">
+      <c r="I13" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="I13" s="1" t="s">
+      <c r="P13" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="P13" s="1" t="s">
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A14" s="1">
+        <v>11</v>
+      </c>
+      <c r="B14" s="1" t="s">
         <v>91</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="I14" s="1" t="s">
+        <v>85</v>
       </c>
     </row>
   </sheetData>

--- a/MMORPG_SERVER/Data/Excel/UnitDefine.xlsx
+++ b/MMORPG_SERVER/Data/Excel/UnitDefine.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\game\MMORPG_GAME_SERVER\MMORPG_SERVER\Data\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9C8BB70-76F1-442C-B1F8-8E7F662E4DF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB652287-3A4B-4981-9B18-845483E93D14}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/MMORPG_SERVER/Data/Excel/UnitDefine.xlsx
+++ b/MMORPG_SERVER/Data/Excel/UnitDefine.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\game\MMORPG_GAME_SERVER\MMORPG_SERVER\Data\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB652287-3A4B-4981-9B18-845483E93D14}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1759B0E-20B1-4635-A03F-679D1D9CB188}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="104">
   <si>
     <t>ID</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -400,6 +400,46 @@
   </si>
   <si>
     <t>Entity/Missile/character1Skill</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>村长</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Npc</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CommunicationId</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>对应对话Id</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>TaskId</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>对应任务Id数组</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[ 2, 3 ]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[ 9, -2, 92 ]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[ 15, -2 ,92 ],[ 0, -2, 92 ]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Entity/Npc/Npc1</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -423,12 +463,36 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -443,15 +507,30 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -734,7 +813,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Q14"/>
+  <dimension ref="A1:S15"/>
   <sheetFormatPr defaultColWidth="17.875" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="5" width="17.875" style="1"/>
@@ -750,7 +829,7 @@
     <col min="17" max="16384" width="17.875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -802,8 +881,14 @@
       <c r="Q1" s="1" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R1" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="2" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>8</v>
       </c>
@@ -855,8 +940,14 @@
       <c r="Q2" s="1" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>10</v>
       </c>
@@ -908,342 +999,374 @@
       <c r="Q3" s="1" t="s">
         <v>83</v>
       </c>
-    </row>
-    <row r="4" spans="1:17" ht="57" x14ac:dyDescent="0.2">
-      <c r="A4" s="1">
+      <c r="R3" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="S3" s="1" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" s="2" customFormat="1" ht="57" x14ac:dyDescent="0.2">
+      <c r="A4" s="2">
         <v>1</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="B4" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="C4" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="D4" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="E4" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="F4" s="1" t="s">
+      <c r="F4" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="G4" s="1">
+      <c r="G4" s="2">
         <v>1200</v>
       </c>
-      <c r="H4" s="1">
+      <c r="H4" s="2">
         <v>80</v>
       </c>
-      <c r="I4" s="1" t="s">
+      <c r="I4" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="L4" s="1" t="s">
+      <c r="L4" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="M4" s="1">
+      <c r="M4" s="2">
         <v>100</v>
       </c>
-      <c r="N4" s="1">
+      <c r="N4" s="2">
         <v>12</v>
       </c>
-      <c r="O4" s="1" t="s">
+      <c r="O4" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="Q4" s="1">
+      <c r="Q4" s="2">
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="1:17" ht="57.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="1">
+    <row r="5" spans="1:19" s="2" customFormat="1" ht="57.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="2">
         <v>2</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="B5" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="C5" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="D5" s="1" t="s">
+      <c r="D5" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="E5" s="2" t="s">
+      <c r="E5" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="F5" s="1" t="s">
+      <c r="F5" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="G5" s="1">
+      <c r="G5" s="2">
         <v>800</v>
       </c>
-      <c r="H5" s="1">
+      <c r="H5" s="2">
         <v>100</v>
       </c>
-      <c r="I5" s="1" t="s">
+      <c r="I5" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="L5" s="1" t="s">
+      <c r="L5" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="M5" s="1">
+      <c r="M5" s="2">
         <v>100</v>
       </c>
-      <c r="N5" s="1">
+      <c r="N5" s="2">
         <v>10</v>
       </c>
-      <c r="O5" s="1" t="s">
+      <c r="O5" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="Q5" s="1">
+      <c r="Q5" s="2">
         <v>8</v>
       </c>
     </row>
-    <row r="6" spans="1:17" ht="56.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="1">
+    <row r="6" spans="1:19" s="2" customFormat="1" ht="56.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="2">
         <v>3</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="B6" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="C6" s="1" t="s">
+      <c r="C6" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="D6" s="1" t="s">
+      <c r="D6" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="E6" s="3" t="s">
+      <c r="E6" s="8" t="s">
         <v>66</v>
       </c>
-      <c r="F6" s="1" t="s">
+      <c r="F6" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="G6" s="1">
+      <c r="G6" s="2">
         <v>1000</v>
       </c>
-      <c r="H6" s="1">
+      <c r="H6" s="2">
         <v>80</v>
       </c>
-      <c r="I6" s="1" t="s">
+      <c r="I6" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="L6" s="1" t="s">
+      <c r="L6" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="M6" s="1">
+      <c r="M6" s="2">
         <v>100</v>
       </c>
-      <c r="N6" s="1">
+      <c r="N6" s="2">
         <v>13</v>
       </c>
-      <c r="O6" s="1" t="s">
+      <c r="O6" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="Q6" s="1">
+      <c r="Q6" s="2">
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:17" ht="62.45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="1">
+    <row r="7" spans="1:19" s="2" customFormat="1" ht="62.45" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="2">
         <v>4</v>
       </c>
-      <c r="B7" s="1" t="s">
+      <c r="B7" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="C7" s="1" t="s">
+      <c r="C7" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="D7" s="1" t="s">
+      <c r="D7" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="E7" s="3" t="s">
+      <c r="E7" s="8" t="s">
         <v>67</v>
       </c>
-      <c r="F7" s="1" t="s">
+      <c r="F7" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="G7" s="1">
+      <c r="G7" s="2">
         <v>1500</v>
       </c>
-      <c r="H7" s="1">
+      <c r="H7" s="2">
         <v>60</v>
       </c>
-      <c r="I7" s="1" t="s">
+      <c r="I7" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="L7" s="1" t="s">
+      <c r="L7" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="M7" s="1">
+      <c r="M7" s="2">
         <v>100</v>
       </c>
-      <c r="N7" s="1">
+      <c r="N7" s="2">
         <v>15</v>
       </c>
-      <c r="O7" s="1" t="s">
+      <c r="O7" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="Q7" s="1">
+      <c r="Q7" s="2">
         <v>9</v>
       </c>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A8" s="1">
+    <row r="8" spans="1:19" s="6" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="6">
         <v>5</v>
       </c>
-      <c r="B8" s="1" t="s">
+      <c r="B8" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="C8" s="1" t="s">
+      <c r="C8" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="F8" s="1" t="s">
+      <c r="F8" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="G8" s="1">
+      <c r="G8" s="6">
         <v>0</v>
       </c>
-      <c r="H8" s="1">
+      <c r="H8" s="6">
         <v>0</v>
       </c>
-      <c r="I8" s="1" t="s">
+      <c r="I8" s="6" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A9" s="1">
+    <row r="9" spans="1:19" s="4" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="4">
         <v>6</v>
       </c>
-      <c r="B9" s="1" t="s">
+      <c r="B9" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="C9" s="1" t="s">
+      <c r="C9" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="F9" s="1" t="s">
+      <c r="F9" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="G9" s="1">
+      <c r="G9" s="4">
         <v>300</v>
       </c>
-      <c r="H9" s="1">
+      <c r="H9" s="4">
         <v>0</v>
       </c>
-      <c r="I9" s="1" t="s">
+      <c r="I9" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="J9" s="1" t="s">
+      <c r="J9" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="K9" s="2" t="s">
+      <c r="K9" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="M9" s="1">
+      <c r="M9" s="4">
         <v>30</v>
       </c>
     </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A10" s="1">
+    <row r="10" spans="1:19" s="4" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="4">
         <v>7</v>
       </c>
-      <c r="B10" s="1" t="s">
+      <c r="B10" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="C10" s="1" t="s">
+      <c r="C10" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="F10" s="1" t="s">
+      <c r="F10" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="G10" s="1">
+      <c r="G10" s="4">
         <v>500</v>
       </c>
-      <c r="H10" s="1">
+      <c r="H10" s="4">
         <v>0</v>
       </c>
-      <c r="I10" s="1" t="s">
+      <c r="I10" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="J10" s="1" t="s">
+      <c r="J10" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="K10" s="2" t="s">
+      <c r="K10" s="5" t="s">
         <v>65</v>
       </c>
-      <c r="M10" s="1">
+      <c r="M10" s="4">
         <v>50</v>
       </c>
     </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A11" s="1">
+    <row r="11" spans="1:19" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="3">
         <v>8</v>
       </c>
-      <c r="B11" s="1" t="s">
+      <c r="B11" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="C11" s="1" t="s">
+      <c r="C11" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="F11" s="1" t="s">
+      <c r="F11" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="I11" s="1" t="s">
+      <c r="I11" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="P11" s="1" t="s">
+      <c r="P11" s="3" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A12" s="1">
+    <row r="12" spans="1:19" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="3">
         <v>9</v>
       </c>
-      <c r="B12" s="1" t="s">
+      <c r="B12" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="C12" s="1" t="s">
+      <c r="C12" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="F12" s="1" t="s">
+      <c r="F12" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="I12" s="1" t="s">
+      <c r="I12" s="3" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A13" s="1">
+    <row r="13" spans="1:19" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="3">
         <v>10</v>
       </c>
-      <c r="B13" s="1" t="s">
+      <c r="B13" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="C13" s="1" t="s">
+      <c r="C13" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="F13" s="1" t="s">
+      <c r="F13" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="I13" s="1" t="s">
+      <c r="I13" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="P13" s="1" t="s">
+      <c r="P13" s="3" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A14" s="1">
+    <row r="14" spans="1:19" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="3">
         <v>11</v>
       </c>
-      <c r="B14" s="1" t="s">
+      <c r="B14" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="C14" s="1" t="s">
+      <c r="C14" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="F14" s="1" t="s">
+      <c r="F14" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="I14" s="1" t="s">
+      <c r="I14" s="3" t="s">
         <v>85</v>
+      </c>
+    </row>
+    <row r="15" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="2">
+        <v>12</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="J15" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="K15" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="R15" s="2">
+        <v>1</v>
+      </c>
+      <c r="S15" s="2" t="s">
+        <v>100</v>
       </c>
     </row>
   </sheetData>

--- a/MMORPG_SERVER/Data/Excel/UnitDefine.xlsx
+++ b/MMORPG_SERVER/Data/Excel/UnitDefine.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\game\MMORPG_GAME_SERVER\MMORPG_SERVER\Data\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1759B0E-20B1-4635-A03F-679D1D9CB188}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FD3F2A7-D247-43A9-A83C-285DA06D89A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="109">
   <si>
     <t>ID</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -427,19 +427,39 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>[ 2, 3 ]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>[ 9, -2, 92 ]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>[ 15, -2 ,92 ],[ 0, -2, 92 ]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>Entity/Npc/Npc1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[ 5, -2, 75 ]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[ [ 1, -2, 83 ],[ 10, -2, 87 ],[ 5, -2, 75 ] ]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[ 2 ]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>媒婆</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Entity/Npc/Npc2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[ -60, 2, 87 ]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[ [ -45, 0, 90], [ -45, 0, 100], [ -60, 2, 87] ]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[ 3, 4 ]</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -813,7 +833,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:S15"/>
+  <dimension ref="A1:S16"/>
   <sheetFormatPr defaultColWidth="17.875" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="5" width="17.875" style="1"/>
@@ -1354,19 +1374,45 @@
         <v>95</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="K15" s="2" t="s">
+      <c r="K15" s="7" t="s">
         <v>102</v>
       </c>
       <c r="R15" s="2">
         <v>1</v>
       </c>
       <c r="S15" s="2" t="s">
-        <v>100</v>
+        <v>103</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A16" s="1">
+        <v>13</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="F16" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="J16" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="K16" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="R16" s="1">
+        <v>2</v>
+      </c>
+      <c r="S16" s="1" t="s">
+        <v>108</v>
       </c>
     </row>
   </sheetData>
